--- a/Templates/Tables/VersionInfo/G_VerInfoTable.xlsx
+++ b/Templates/Tables/VersionInfo/G_VerInfoTable.xlsx
@@ -18,13 +18,13 @@
     <t>NOEX_Description</t>
   </si>
   <si>
-    <t>True_01</t>
+    <t>Flags_01</t>
   </si>
   <si>
-    <t>True_02</t>
+    <t>Flags_02</t>
   </si>
   <si>
-    <t>True_03</t>
+    <t>Flags_03</t>
   </si>
   <si>
     <t>Name</t>
@@ -140,7 +140,7 @@
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" vertical="bottom"/>
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -366,8 +366,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="4" width="7.13"/>
+    <col customWidth="1" min="1" max="1" width="16.88"/>
+    <col customWidth="1" min="2" max="4" width="7.88"/>
     <col customWidth="1" min="5" max="5" width="15.75"/>
     <col customWidth="1" min="6" max="6" width="4.75"/>
     <col customWidth="1" min="7" max="26" width="12.63"/>
@@ -6785,8 +6785,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="4" width="7.13"/>
+    <col customWidth="1" min="1" max="1" width="16.88"/>
+    <col customWidth="1" min="2" max="4" width="7.88"/>
     <col customWidth="1" min="5" max="5" width="15.75"/>
     <col customWidth="1" min="6" max="6" width="4.75"/>
     <col customWidth="1" min="7" max="26" width="12.63"/>
@@ -13204,8 +13204,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="4" width="7.13"/>
+    <col customWidth="1" min="1" max="1" width="16.88"/>
+    <col customWidth="1" min="2" max="4" width="7.88"/>
     <col customWidth="1" min="5" max="5" width="15.75"/>
     <col customWidth="1" min="6" max="6" width="4.75"/>
     <col customWidth="1" min="7" max="26" width="12.63"/>
